--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,25 +55,37 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>В3270ВН</t>
   </si>
   <si>
+    <t>В4450ТТ</t>
+  </si>
+  <si>
     <t>78970155027721152</t>
   </si>
   <si>
+    <t>78970155027721160</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:44:00</t>
-  </si>
-  <si>
-    <t>3236622748 3236622748</t>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>17:41</t>
+  </si>
+  <si>
+    <t>15:32</t>
+  </si>
+  <si>
+    <t>09:22</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -499,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,17 +517,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,125 +566,242 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>74.27</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="H2" s="1">
+        <v>134.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="J2" s="1">
+        <v>136.657</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>187500</v>
+      </c>
+      <c r="M2">
+        <v>297626</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>57.61</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.83</v>
+      </c>
+      <c r="H3" s="1">
+        <v>105.426</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="J3" s="1">
+        <v>107.155</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3">
+        <v>50020</v>
+      </c>
+      <c r="M3">
+        <v>298367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="F2">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>24.78</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.83</v>
+      </c>
+      <c r="H4" s="1">
+        <v>45.347</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46.091</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
+        <v>187700</v>
+      </c>
+      <c r="M4">
+        <v>298653</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="I2" s="1">
-        <v>127.967</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="K2" s="1">
-        <v>130.112</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="M2">
-        <v>186883</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
+      <c r="F5">
+        <v>45.92</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.89</v>
+      </c>
+      <c r="H5" s="1">
+        <v>86.789</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.92</v>
+      </c>
+      <c r="J5" s="1">
+        <v>88.166</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5">
+        <v>50430</v>
+      </c>
+      <c r="M5">
+        <v>256855</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
+      <c r="B9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9">
-        <v>1.79</v>
-      </c>
-      <c r="E7" s="7">
-        <v>127.97</v>
-      </c>
-      <c r="F7" s="7">
-        <v>130.11</v>
+    <row r="10" spans="1:13">
+      <c r="A10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>202.58</v>
+      </c>
+      <c r="C10" s="8">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.83627</v>
+      </c>
+      <c r="E10" s="7">
+        <v>371.99</v>
+      </c>
+      <c r="F10" s="7">
+        <v>378.07</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="11">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="11">
-        <v>127.97</v>
-      </c>
-      <c r="F8" s="11">
-        <v>130.11</v>
+    <row r="11" spans="1:13">
+      <c r="A11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11">
+        <v>202.58</v>
+      </c>
+      <c r="C11" s="12">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="11">
+        <v>371.99</v>
+      </c>
+      <c r="F11" s="11">
+        <v>378.07</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
